--- a/research/traditional_assets/database/data/kuwait/kuwait_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_oil_gas_integrated.xlsx
@@ -588,118 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.258</v>
+        <v>-0.4320000000000001</v>
       </c>
       <c r="G2">
-        <v>-1.059405940594059</v>
+        <v>-1.28</v>
       </c>
       <c r="H2">
-        <v>-1.059405940594059</v>
+        <v>-1.28</v>
       </c>
       <c r="I2">
-        <v>-0.4782178217821783</v>
+        <v>-1.531428571428572</v>
       </c>
       <c r="J2">
-        <v>-0.2592296215922963</v>
+        <v>-1.531428571428572</v>
       </c>
       <c r="K2">
-        <v>6.65</v>
+        <v>-40.1</v>
       </c>
       <c r="L2">
-        <v>0.6584158415841584</v>
+        <v>-22.91428571428571</v>
       </c>
       <c r="M2">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.001143769968051118</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.0269172932330827</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.001143769968051118</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.0269172932330827</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>51.2</v>
+        <v>54.4</v>
       </c>
       <c r="V2">
-        <v>0.3271565495207668</v>
+        <v>1.034220532319392</v>
       </c>
       <c r="W2">
-        <v>0.08514724711907812</v>
+        <v>-0.5905743740795287</v>
       </c>
       <c r="X2">
-        <v>0.06929279235114107</v>
+        <v>0.1132789181904143</v>
       </c>
       <c r="Y2">
-        <v>0.01585445476793705</v>
+        <v>-0.7038532922699431</v>
       </c>
       <c r="Z2">
-        <v>0.4486894713460685</v>
+        <v>0.100080064051241</v>
       </c>
       <c r="AA2">
-        <v>-0.1163136018694888</v>
+        <v>-0.1532654695184719</v>
       </c>
       <c r="AB2">
-        <v>0.06909073204899677</v>
+        <v>0.1122005609030953</v>
       </c>
       <c r="AC2">
-        <v>-0.1854043339184855</v>
+        <v>-0.2654660304215672</v>
       </c>
       <c r="AD2">
-        <v>0.786</v>
+        <v>0.976</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.786</v>
+        <v>0.976</v>
       </c>
       <c r="AG2">
-        <v>-50.414</v>
+        <v>-53.424</v>
       </c>
       <c r="AH2">
-        <v>0.004997266126673703</v>
+        <v>0.01821711213976407</v>
       </c>
       <c r="AI2">
-        <v>0.01065242728972976</v>
+        <v>0.01461602971127351</v>
       </c>
       <c r="AJ2">
-        <v>-0.4752182191806648</v>
+        <v>64.83495145631083</v>
       </c>
       <c r="AK2">
-        <v>-2.232090675639777</v>
+        <v>-4.316742081447964</v>
       </c>
       <c r="AL2">
-        <v>0.103</v>
+        <v>0.068</v>
       </c>
       <c r="AM2">
-        <v>-0.723</v>
+        <v>-0.863</v>
       </c>
       <c r="AN2">
-        <v>-0.1627329192546584</v>
+        <v>-0.3683018867924528</v>
       </c>
       <c r="AO2">
-        <v>-46.89320388349515</v>
+        <v>-39.41176470588236</v>
       </c>
       <c r="AP2">
-        <v>10.43768115942029</v>
+        <v>20.16</v>
       </c>
       <c r="AQ2">
-        <v>6.680497925311204</v>
+        <v>3.105446118192353</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +716,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.258</v>
+        <v>-0.4320000000000001</v>
       </c>
       <c r="G3">
-        <v>-1.059405940594059</v>
+        <v>-1.28</v>
       </c>
       <c r="H3">
-        <v>-1.059405940594059</v>
+        <v>-1.28</v>
       </c>
       <c r="I3">
-        <v>-0.4782178217821783</v>
+        <v>-1.531428571428572</v>
       </c>
       <c r="J3">
-        <v>-0.2592296215922963</v>
+        <v>-1.531428571428572</v>
       </c>
       <c r="K3">
-        <v>6.65</v>
+        <v>-40.1</v>
       </c>
       <c r="L3">
-        <v>0.6584158415841584</v>
+        <v>-22.91428571428571</v>
       </c>
       <c r="M3">
-        <v>0.179</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.001143769968051118</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.0269172932330827</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.179</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.001143769968051118</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.0269172932330827</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>51.2</v>
+        <v>54.4</v>
       </c>
       <c r="V3">
-        <v>0.3271565495207668</v>
+        <v>1.034220532319392</v>
       </c>
       <c r="W3">
-        <v>0.08514724711907812</v>
+        <v>-0.5905743740795287</v>
       </c>
       <c r="X3">
-        <v>0.06929279235114107</v>
+        <v>0.1132789181904143</v>
       </c>
       <c r="Y3">
-        <v>0.01585445476793705</v>
+        <v>-0.7038532922699431</v>
       </c>
       <c r="Z3">
-        <v>0.4486894713460685</v>
+        <v>0.100080064051241</v>
       </c>
       <c r="AA3">
-        <v>-0.1163136018694888</v>
+        <v>-0.1532654695184719</v>
       </c>
       <c r="AB3">
-        <v>0.06909073204899677</v>
+        <v>0.1122005609030953</v>
       </c>
       <c r="AC3">
-        <v>-0.1854043339184855</v>
+        <v>-0.2654660304215672</v>
       </c>
       <c r="AD3">
-        <v>0.786</v>
+        <v>0.976</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.786</v>
+        <v>0.976</v>
       </c>
       <c r="AG3">
-        <v>-50.414</v>
+        <v>-53.424</v>
       </c>
       <c r="AH3">
-        <v>0.004997266126673703</v>
+        <v>0.01821711213976407</v>
       </c>
       <c r="AI3">
-        <v>0.01065242728972976</v>
+        <v>0.01461602971127351</v>
       </c>
       <c r="AJ3">
-        <v>-0.4752182191806648</v>
+        <v>64.83495145631083</v>
       </c>
       <c r="AK3">
-        <v>-2.232090675639777</v>
+        <v>-4.316742081447964</v>
       </c>
       <c r="AL3">
-        <v>0.103</v>
+        <v>0.068</v>
       </c>
       <c r="AM3">
-        <v>-0.723</v>
+        <v>-0.863</v>
       </c>
       <c r="AN3">
-        <v>-0.1627329192546584</v>
+        <v>-0.3683018867924528</v>
       </c>
       <c r="AO3">
-        <v>-46.89320388349515</v>
+        <v>-39.41176470588236</v>
       </c>
       <c r="AP3">
-        <v>10.43768115942029</v>
+        <v>20.16</v>
       </c>
       <c r="AQ3">
-        <v>6.680497925311204</v>
+        <v>3.105446118192353</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_oil_gas_integrated.xlsx
@@ -588,115 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.4320000000000001</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="G2">
-        <v>-1.28</v>
+        <v>-31.53846153846154</v>
       </c>
       <c r="H2">
-        <v>-1.28</v>
+        <v>-31.53846153846154</v>
       </c>
       <c r="I2">
-        <v>-1.531428571428572</v>
+        <v>-31.41025641025641</v>
       </c>
       <c r="J2">
-        <v>-1.531428571428572</v>
+        <v>-31.41025641025641</v>
       </c>
       <c r="K2">
-        <v>-40.1</v>
+        <v>0.705</v>
       </c>
       <c r="L2">
-        <v>-22.91428571428571</v>
+        <v>9.038461538461538</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>5.53763440860215</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>73.04964539007092</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>5.53763440860215</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>73.04964539007092</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>54.4</v>
+        <v>10.5</v>
       </c>
       <c r="V2">
-        <v>1.034220532319392</v>
+        <v>1.129032258064516</v>
       </c>
       <c r="W2">
-        <v>-0.5905743740795287</v>
+        <v>0.0106015037593985</v>
       </c>
       <c r="X2">
-        <v>0.1132789181904143</v>
+        <v>0.09177599166834399</v>
       </c>
       <c r="Y2">
-        <v>-0.7038532922699431</v>
+        <v>-0.08117448790894549</v>
       </c>
       <c r="Z2">
-        <v>0.100080064051241</v>
+        <v>0.005965126950137656</v>
       </c>
       <c r="AA2">
-        <v>-0.1532654695184719</v>
+        <v>-0.1873661670235546</v>
       </c>
       <c r="AB2">
-        <v>0.1122005609030953</v>
+        <v>0.09147098638364183</v>
       </c>
       <c r="AC2">
-        <v>-0.2654660304215672</v>
+        <v>-0.2788371534071964</v>
       </c>
       <c r="AD2">
-        <v>0.976</v>
+        <v>0.068</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.976</v>
+        <v>0.068</v>
       </c>
       <c r="AG2">
-        <v>-53.424</v>
+        <v>-10.432</v>
       </c>
       <c r="AH2">
-        <v>0.01821711213976407</v>
+        <v>0.007258753202391119</v>
       </c>
       <c r="AI2">
-        <v>0.01461602971127351</v>
+        <v>0.004833665055444982</v>
       </c>
       <c r="AJ2">
-        <v>64.83495145631083</v>
+        <v>9.215547703180215</v>
       </c>
       <c r="AK2">
-        <v>-4.316742081447964</v>
+        <v>-2.923766816143498</v>
       </c>
       <c r="AL2">
-        <v>0.068</v>
+        <v>0.039</v>
       </c>
       <c r="AM2">
-        <v>-0.863</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="AN2">
-        <v>-0.3683018867924528</v>
+        <v>-0.0278688524590164</v>
       </c>
       <c r="AO2">
-        <v>-39.41176470588236</v>
+        <v>-62.82051282051282</v>
       </c>
       <c r="AP2">
-        <v>20.16</v>
+        <v>4.275409836065574</v>
       </c>
       <c r="AQ2">
-        <v>3.105446118192353</v>
+        <v>3.555878084179971</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.4320000000000001</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="G3">
-        <v>-1.28</v>
+        <v>-31.53846153846154</v>
       </c>
       <c r="H3">
-        <v>-1.28</v>
+        <v>-31.53846153846154</v>
       </c>
       <c r="I3">
-        <v>-1.531428571428572</v>
+        <v>-31.41025641025641</v>
       </c>
       <c r="J3">
-        <v>-1.531428571428572</v>
+        <v>-31.41025641025641</v>
       </c>
       <c r="K3">
-        <v>-40.1</v>
+        <v>0.705</v>
       </c>
       <c r="L3">
-        <v>-22.91428571428571</v>
+        <v>9.038461538461538</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>51.5</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>5.53763440860215</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>73.04964539007092</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>51.5</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>5.53763440860215</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>73.04964539007092</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>54.4</v>
+        <v>10.5</v>
       </c>
       <c r="V3">
-        <v>1.034220532319392</v>
+        <v>1.129032258064516</v>
       </c>
       <c r="W3">
-        <v>-0.5905743740795287</v>
+        <v>0.0106015037593985</v>
       </c>
       <c r="X3">
-        <v>0.1132789181904143</v>
+        <v>0.09177599166834399</v>
       </c>
       <c r="Y3">
-        <v>-0.7038532922699431</v>
+        <v>-0.08117448790894549</v>
       </c>
       <c r="Z3">
-        <v>0.100080064051241</v>
+        <v>0.005965126950137656</v>
       </c>
       <c r="AA3">
-        <v>-0.1532654695184719</v>
+        <v>-0.1873661670235546</v>
       </c>
       <c r="AB3">
-        <v>0.1122005609030953</v>
+        <v>0.09147098638364183</v>
       </c>
       <c r="AC3">
-        <v>-0.2654660304215672</v>
+        <v>-0.2788371534071964</v>
       </c>
       <c r="AD3">
-        <v>0.976</v>
+        <v>0.068</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.976</v>
+        <v>0.068</v>
       </c>
       <c r="AG3">
-        <v>-53.424</v>
+        <v>-10.432</v>
       </c>
       <c r="AH3">
-        <v>0.01821711213976407</v>
+        <v>0.007258753202391119</v>
       </c>
       <c r="AI3">
-        <v>0.01461602971127351</v>
+        <v>0.004833665055444982</v>
       </c>
       <c r="AJ3">
-        <v>64.83495145631083</v>
+        <v>9.215547703180215</v>
       </c>
       <c r="AK3">
-        <v>-4.316742081447964</v>
+        <v>-2.923766816143498</v>
       </c>
       <c r="AL3">
-        <v>0.068</v>
+        <v>0.039</v>
       </c>
       <c r="AM3">
-        <v>-0.863</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="AN3">
-        <v>-0.3683018867924528</v>
+        <v>-0.0278688524590164</v>
       </c>
       <c r="AO3">
-        <v>-39.41176470588236</v>
+        <v>-62.82051282051282</v>
       </c>
       <c r="AP3">
-        <v>20.16</v>
+        <v>4.275409836065574</v>
       </c>
       <c r="AQ3">
-        <v>3.105446118192353</v>
+        <v>3.555878084179971</v>
       </c>
     </row>
   </sheetData>
